--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41DF781E-3BAF-4A5C-85DB-7935F97FBAED}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB62B0ED-8E84-4B64-A301-BE287DA40192}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-20" windowWidth="38620" windowHeight="21100" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="6730" yWindow="1960" windowWidth="28800" windowHeight="17680" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -248,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -266,6 +266,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -684,8 +685,8 @@
       <c r="I3">
         <v>1</v>
       </c>
-      <c r="K3">
-        <v>2</v>
+      <c r="K3" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -719,6 +720,9 @@
       <c r="J4" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -781,6 +785,9 @@
         <v>34</v>
       </c>
       <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
         <v>1</v>
       </c>
     </row>
@@ -815,6 +822,9 @@
       <c r="J7" s="8" t="s">
         <v>35</v>
       </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
@@ -844,8 +854,8 @@
       <c r="I8">
         <v>6</v>
       </c>
-      <c r="K8" s="2">
-        <v>1</v>
+      <c r="K8" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -905,7 +915,9 @@
       <c r="D13" s="4">
         <v>5</v>
       </c>
-      <c r="E13" s="4"/>
+      <c r="E13">
+        <v>2</v>
+      </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -924,7 +936,9 @@
       <c r="D14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14">
+        <v>1</v>
+      </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -943,7 +957,9 @@
       <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15">
+        <v>6</v>
+      </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -962,7 +978,9 @@
       <c r="D16">
         <v>2</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16">
+        <v>5</v>
+      </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -981,7 +999,9 @@
       <c r="D17" s="5">
         <v>3</v>
       </c>
-      <c r="E17" s="4"/>
+      <c r="E17" s="2">
+        <v>7</v>
+      </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -1000,7 +1020,9 @@
       <c r="D18" s="4">
         <v>4</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18">
+        <v>3</v>
+      </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -1017,7 +1039,9 @@
       <c r="D19" s="5">
         <v>6</v>
       </c>
-      <c r="E19" s="4"/>
+      <c r="E19">
+        <v>4</v>
+      </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -1033,8 +1057,8 @@
         <v>1</v>
       </c>
       <c r="B23" cm="1">
-        <f t="array" aca="1" ref="B23:B25" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(3), _xlfn.RANDARRAY(3))</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="B23:B29" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(7), _xlfn.RANDARRAY(7))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1043,7 +1067,7 @@
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1052,27 +1076,43 @@
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="B26">
+        <f ca="1"/>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B27">
+        <f ca="1"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="B28">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="B29">
+        <f ca="1"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB62B0ED-8E84-4B64-A301-BE287DA40192}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{527FABAB-FFD4-441E-A273-BF7D82B046F8}"/>
   <bookViews>
-    <workbookView xWindow="6730" yWindow="1960" windowWidth="28800" windowHeight="17680" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="-38510" yWindow="-20" windowWidth="38620" windowHeight="21100" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
   <si>
     <t>Vessel</t>
   </si>
@@ -248,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -266,7 +266,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -854,7 +853,7 @@
       <c r="I8">
         <v>6</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8">
         <v>2</v>
       </c>
     </row>
@@ -1000,7 +999,7 @@
         <v>3</v>
       </c>
       <c r="E17" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -1039,8 +1038,8 @@
       <c r="D19" s="5">
         <v>6</v>
       </c>
-      <c r="E19">
-        <v>4</v>
+      <c r="E19" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -1058,7 +1057,7 @@
       </c>
       <c r="B23" cm="1">
         <f t="array" aca="1" ref="B23:B29" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(7), _xlfn.RANDARRAY(7))</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1067,7 +1066,7 @@
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1085,7 +1084,7 @@
       </c>
       <c r="B26">
         <f ca="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1094,7 +1093,7 @@
       </c>
       <c r="B27">
         <f ca="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1103,7 +1102,7 @@
       </c>
       <c r="B28">
         <f ca="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{527FABAB-FFD4-441E-A273-BF7D82B046F8}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8383ED53-CFCF-4DBD-9D3A-8DE5EC4B49C4}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-20" windowWidth="38620" windowHeight="21100" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -248,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -266,6 +266,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -719,7 +720,7 @@
       <c r="J4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="2">
         <v>1</v>
       </c>
     </row>
@@ -787,7 +788,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -821,9 +822,6 @@
       <c r="J7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
@@ -855,6 +853,9 @@
       </c>
       <c r="K8">
         <v>2</v>
+      </c>
+      <c r="L8" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -1056,8 +1057,8 @@
         <v>1</v>
       </c>
       <c r="B23" cm="1">
-        <f t="array" aca="1" ref="B23:B29" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(7), _xlfn.RANDARRAY(7))</f>
-        <v>1</v>
+        <f t="array" aca="1" ref="B23:B25" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(3), _xlfn.RANDARRAY(3))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1066,7 +1067,7 @@
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1075,43 +1076,27 @@
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B26">
-        <f ca="1"/>
-        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B27">
-        <f ca="1"/>
-        <v>6</v>
-      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B28">
-        <f ca="1"/>
-        <v>4</v>
-      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B29">
-        <f ca="1"/>
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8383ED53-CFCF-4DBD-9D3A-8DE5EC4B49C4}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13E97CF0-6501-4AC8-9F7A-6F9C29DBA764}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="1340" yWindow="490" windowWidth="34680" windowHeight="20300" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="42">
   <si>
     <t>Vessel</t>
   </si>
@@ -129,9 +129,6 @@
     <t>SB10</t>
   </si>
   <si>
-    <t>SB11</t>
-  </si>
-  <si>
     <t>GB1</t>
   </si>
   <si>
@@ -153,9 +150,6 @@
     <t>GB7</t>
   </si>
   <si>
-    <t>GB8</t>
-  </si>
-  <si>
     <t>(1)</t>
   </si>
   <si>
@@ -187,6 +181,12 @@
   </si>
   <si>
     <t>*5</t>
+  </si>
+  <si>
+    <t>6*</t>
+  </si>
+  <si>
+    <t>SB11 - Cancelled</t>
   </si>
 </sst>
 </file>
@@ -222,7 +222,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -232,6 +232,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -266,7 +272,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -610,7 +616,7 @@
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -653,8 +659,8 @@
       <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>22</v>
+      <c r="L2" s="9" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -662,16 +668,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -685,8 +691,8 @@
       <c r="I3">
         <v>1</v>
       </c>
-      <c r="K3" s="2">
-        <v>1</v>
+      <c r="K3" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -706,10 +712,10 @@
         <v>5</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -718,7 +724,7 @@
         <v>4</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L4" s="2">
         <v>1</v>
@@ -747,10 +753,10 @@
         <v>1</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K5">
         <v>3</v>
@@ -782,7 +788,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -817,10 +823,10 @@
         <v>3</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -846,7 +852,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I8">
         <v>6</v>
@@ -854,7 +860,7 @@
       <c r="K8">
         <v>2</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8">
         <v>3</v>
       </c>
     </row>
@@ -864,7 +870,7 @@
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -878,29 +884,27 @@
         <v>0</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
@@ -918,7 +922,9 @@
       <c r="E13">
         <v>2</v>
       </c>
-      <c r="F13" s="4"/>
+      <c r="F13" s="4">
+        <v>5</v>
+      </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -934,12 +940,14 @@
         <v>5</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14" s="4"/>
+      <c r="F14" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -960,7 +968,9 @@
       <c r="E15">
         <v>6</v>
       </c>
-      <c r="F15" s="4"/>
+      <c r="F15" s="4">
+        <v>2</v>
+      </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -973,7 +983,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -981,7 +991,9 @@
       <c r="E16">
         <v>5</v>
       </c>
-      <c r="F16" s="4"/>
+      <c r="F16" s="4">
+        <v>3</v>
+      </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -991,7 +1003,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C17" s="4">
         <v>4</v>
@@ -1002,7 +1014,9 @@
       <c r="E17" s="2">
         <v>4</v>
       </c>
-      <c r="F17" s="4"/>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -1012,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C18" s="4">
         <v>2</v>
@@ -1023,7 +1037,9 @@
       <c r="E18">
         <v>3</v>
       </c>
-      <c r="F18" s="4"/>
+      <c r="F18" s="4">
+        <v>4</v>
+      </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -1040,7 +1056,7 @@
         <v>6</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -1057,8 +1073,8 @@
         <v>1</v>
       </c>
       <c r="B23" cm="1">
-        <f t="array" aca="1" ref="B23:B25" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(3), _xlfn.RANDARRAY(3))</f>
-        <v>3</v>
+        <f t="array" aca="1" ref="B23:B28" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(6), _xlfn.RANDARRAY(6))</f>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1067,7 +1083,7 @@
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1083,15 +1099,27 @@
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B26">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="B27">
+        <f ca="1"/>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="B28">
+        <f ca="1"/>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="147" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13E97CF0-6501-4AC8-9F7A-6F9C29DBA764}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E67EEBE-C4D2-442B-9B4D-B2822BBE9F5E}"/>
   <bookViews>
-    <workbookView xWindow="1340" yWindow="490" windowWidth="34680" windowHeight="20300" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -925,8 +925,9 @@
       <c r="F13" s="4">
         <v>5</v>
       </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
@@ -948,8 +949,9 @@
       <c r="F14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="G14" s="4">
+        <v>5</v>
+      </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -971,8 +973,9 @@
       <c r="F15" s="4">
         <v>2</v>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="G15" s="4">
+        <v>4</v>
+      </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
@@ -994,8 +997,9 @@
       <c r="F16" s="4">
         <v>3</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="G16" s="4">
+        <v>3</v>
+      </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1017,8 +1021,9 @@
       <c r="F17" s="5">
         <v>1</v>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="G17" s="4">
+        <v>2</v>
+      </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -1040,8 +1045,9 @@
       <c r="F18" s="4">
         <v>4</v>
       </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="G18" s="4">
+        <v>6</v>
+      </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -1074,7 +1080,7 @@
       </c>
       <c r="B23" cm="1">
         <f t="array" aca="1" ref="B23:B28" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(6), _xlfn.RANDARRAY(6))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1083,7 +1089,7 @@
       </c>
       <c r="B24">
         <f ca="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1092,7 +1098,7 @@
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1101,7 +1107,7 @@
       </c>
       <c r="B26">
         <f ca="1"/>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1110,7 +1116,7 @@
       </c>
       <c r="B27">
         <f ca="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1119,7 +1125,7 @@
       </c>
       <c r="B28">
         <f ca="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">

--- a/Surveys/2026/2026 Vessel survey order.xlsx
+++ b/Surveys/2026/2026 Vessel survey order.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E67EEBE-C4D2-442B-9B4D-B2822BBE9F5E}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="13_ncr:1_{03C5214E-6F9C-4314-83D6-A89098EEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{531D5921-2DBE-4F01-8A23-AD826F01584A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
+    <workbookView xWindow="1960" yWindow="3140" windowWidth="36310" windowHeight="15450" xr2:uid="{42A79B7A-1230-4D02-8BB7-D807B792038E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="42">
   <si>
     <t>Vessel</t>
   </si>
@@ -726,8 +726,8 @@
       <c r="J4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="2">
-        <v>1</v>
+      <c r="L4" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -925,8 +925,11 @@
       <c r="F13" s="4">
         <v>5</v>
       </c>
-      <c r="G13" s="5">
-        <v>1</v>
+      <c r="G13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="I13" s="4"/>
     </row>
@@ -952,6 +955,9 @@
       <c r="G14" s="4">
         <v>5</v>
       </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -976,6 +982,9 @@
       <c r="G15" s="4">
         <v>4</v>
       </c>
+      <c r="H15" s="4">
+        <v>2</v>
+      </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
@@ -1000,6 +1009,9 @@
       <c r="G16" s="4">
         <v>3</v>
       </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1023,6 +1035,9 @@
       </c>
       <c r="G17" s="4">
         <v>2</v>
+      </c>
+      <c r="H17">
+        <v>4</v>
       </c>
       <c r="I17" s="4"/>
     </row>
@@ -1079,8 +1094,8 @@
         <v>1</v>
       </c>
       <c r="B23" cm="1">
-        <f t="array" aca="1" ref="B23:B28" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(6), _xlfn.RANDARRAY(6))</f>
-        <v>3</v>
+        <f t="array" aca="1" ref="B23:B27" ca="1" xml:space="preserve"> _xlfn.SORTBY(_xlfn.SEQUENCE(5), _xlfn.RANDARRAY(5))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1098,7 +1113,7 @@
       </c>
       <c r="B25">
         <f ca="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1107,7 +1122,7 @@
       </c>
       <c r="B26">
         <f ca="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1116,16 +1131,12 @@
       </c>
       <c r="B27">
         <f ca="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B28">
-        <f ca="1"/>
-        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
